--- a/groups.xlsx
+++ b/groups.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mini Project List" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +53,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,77 +440,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>M1 Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>M1 PRN</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>M1 Div</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>M2 Name</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>M2 PRN</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>M2 Div</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>M3 Name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>M3 PRN</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>M3 Div</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>M4 Name</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>M4 PRN</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>M4 Div</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sandip University, Nashik (MS), India</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Program: B.Tech CSE | Sem IV | Div A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Microcontroller &amp; Interfacing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mini Project List</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sr.No</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>PRN No</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Project Group Members</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Project Title</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>